--- a/documentacao/Testes/Caso de Teste/UC04   - Minhas Consultas.xlsx
+++ b/documentacao/Testes/Caso de Teste/UC04   - Minhas Consultas.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IFCE\Documents\GitHub\taximix\chekout\plataformainclua\documentacao\Testes\Caso de Teste\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B2C4C7-7C14-4A3E-9419-8C703ED01E35}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
@@ -20,214 +25,214 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="66">
-  <si>
-    <t xml:space="preserve">Caso de Teste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dados de Entrada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resultado Esperado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resultado Obtido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status (OK/NOK)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observações</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT01 - Acessar Página de Consultas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Autenticar como paciente.2. Navegar no menu lateral e clicar em "Minhas Consultas".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paciente autenticado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Página "Minhas Consultas" é carregada com a tabela de consultas agendadas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT02 - Exibir Lista de Consultas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Acessar a página "Minhas Consultas".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consultas agendadas existentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabela exibe colunas: Paciente, Horário Agendado, Dia, Médico, Especialidade, Clínica e Ações (Cancelar/Pagar).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT03 - Nenhuma Consulta Encontrada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Acessar a página "Minhas Consultas" sem consultas cadastradas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nenhuma consulta agendada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mensagem exibida: "Nenhuma consulta agendada encontrada."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT04 - Cancelar Consulta com Sucesso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Clicar em "Cancelar" em uma consulta específica.2. Confirmar cancelamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consulta agendada válida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status atualizado para "Cancelada". Tabela atualizada automaticamente. Notificação enviada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT05 - Cancelamento Não Confirmado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Clicar em "Cancelar".2. Não confirmar a ação.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Popup fechado e nenhuma alteração realizada na consulta.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT06 - Cancelar Consulta Já Cancelada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Tentar cancelar uma consulta já cancelada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consulta com status "Cancelada"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mensagem: "Esta consulta já foi cancelada anteriormente."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT07 - Realizar Pagamento com Sucesso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Clicar em "Pagar" em uma consulta específica.2. Selecionar método de pagamento.3. Inserir dados e confirmar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dados de cartão válidos ou link de pagamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagamento processado com sucesso, status atualizado para "Paga". Confirmação exibida e tabela atualizada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT08 - Falha no Pagamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Clicar em "Pagar".2. Inserir dados inválidos ou transação recusada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dados incorretos / Cartão recusado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mensagem: "Pagamento não autorizado. Tente novamente ou use outro método." e opção de repetir processo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT09 - Pagar Consulta Já Paga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Tentar pagar uma consulta com status "Paga".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consulta já paga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mensagem exibida: "Esta consulta já está com pagamento confirmado."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT10 - Sessão de Pagamento Expirada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Iniciar pagamento.2. Aguardar mais de 15 minutos sem ação.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sessão inativa por &gt; 15 min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sessão expira e sistema exige reinício do processo de pagamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT11 - Cancelamento Após Prazo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Tentar cancelar consulta com menos de 24h de antecedência.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consulta fora do prazo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sistema informa sobre possível multa conforme política da clínica.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT12 - Atualização da Tabela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Concluir cancelamento ou pagamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabela de consultas atualizada automaticamente com novo status.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT13 - Geração de Log Financeiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Realizar um pagamento com sucesso.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dados de pagamento válidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log financeiro gerado para a transação.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT14 - Envio de Notificações</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Cancelar ou pagar uma consulta.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-mail enviado automaticamente ao paciente e à clínica.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT15 - Segurança de Dados no Pagamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Realizar pagamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dados do cartão</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dados sensíveis não armazenados. Transação realizada via tokenização.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="67">
+  <si>
+    <t>Caso de Teste</t>
+  </si>
+  <si>
+    <t>Passos</t>
+  </si>
+  <si>
+    <t>Dados de Entrada</t>
+  </si>
+  <si>
+    <t>Resultado Esperado</t>
+  </si>
+  <si>
+    <t>Resultado Obtido</t>
+  </si>
+  <si>
+    <t>Status (OK/NOK)</t>
+  </si>
+  <si>
+    <t>Observações</t>
+  </si>
+  <si>
+    <t>CT01 - Acessar Página de Consultas</t>
+  </si>
+  <si>
+    <t>1. Autenticar como paciente.2. Navegar no menu lateral e clicar em "Minhas Consultas".</t>
+  </si>
+  <si>
+    <t>Paciente autenticado</t>
+  </si>
+  <si>
+    <t>Página "Minhas Consultas" é carregada com a tabela de consultas agendadas.</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>CT02 - Exibir Lista de Consultas</t>
+  </si>
+  <si>
+    <t>1. Acessar a página "Minhas Consultas".</t>
+  </si>
+  <si>
+    <t>Consultas agendadas existentes</t>
+  </si>
+  <si>
+    <t>Tabela exibe colunas: Paciente, Horário Agendado, Dia, Médico, Especialidade, Clínica e Ações (Cancelar/Pagar).</t>
+  </si>
+  <si>
+    <t>CT03 - Nenhuma Consulta Encontrada</t>
+  </si>
+  <si>
+    <t>1. Acessar a página "Minhas Consultas" sem consultas cadastradas.</t>
+  </si>
+  <si>
+    <t>Nenhuma consulta agendada</t>
+  </si>
+  <si>
+    <t>Mensagem exibida: "Nenhuma consulta agendada encontrada."</t>
+  </si>
+  <si>
+    <t>CT04 - Cancelar Consulta com Sucesso</t>
+  </si>
+  <si>
+    <t>1. Clicar em "Cancelar" em uma consulta específica.2. Confirmar cancelamento.</t>
+  </si>
+  <si>
+    <t>Consulta agendada válida</t>
+  </si>
+  <si>
+    <t>Status atualizado para "Cancelada". Tabela atualizada automaticamente. Notificação enviada.</t>
+  </si>
+  <si>
+    <t>CT05 - Cancelamento Não Confirmado</t>
+  </si>
+  <si>
+    <t>1. Clicar em "Cancelar".2. Não confirmar a ação.</t>
+  </si>
+  <si>
+    <t>Popup fechado e nenhuma alteração realizada na consulta.</t>
+  </si>
+  <si>
+    <t>CT06 - Cancelar Consulta Já Cancelada</t>
+  </si>
+  <si>
+    <t>1. Tentar cancelar uma consulta já cancelada.</t>
+  </si>
+  <si>
+    <t>Consulta com status "Cancelada"</t>
+  </si>
+  <si>
+    <t>Mensagem: "Esta consulta já foi cancelada anteriormente."</t>
+  </si>
+  <si>
+    <t>CT07 - Realizar Pagamento com Sucesso</t>
+  </si>
+  <si>
+    <t>1. Clicar em "Pagar" em uma consulta específica.2. Selecionar método de pagamento.3. Inserir dados e confirmar.</t>
+  </si>
+  <si>
+    <t>Dados de cartão válidos ou link de pagamento</t>
+  </si>
+  <si>
+    <t>Pagamento processado com sucesso, status atualizado para "Paga". Confirmação exibida e tabela atualizada.</t>
+  </si>
+  <si>
+    <t>CT08 - Falha no Pagamento</t>
+  </si>
+  <si>
+    <t>1. Clicar em "Pagar".2. Inserir dados inválidos ou transação recusada.</t>
+  </si>
+  <si>
+    <t>Dados incorretos / Cartão recusado</t>
+  </si>
+  <si>
+    <t>Mensagem: "Pagamento não autorizado. Tente novamente ou use outro método." e opção de repetir processo.</t>
+  </si>
+  <si>
+    <t>CT09 - Pagar Consulta Já Paga</t>
+  </si>
+  <si>
+    <t>1. Tentar pagar uma consulta com status "Paga".</t>
+  </si>
+  <si>
+    <t>Consulta já paga</t>
+  </si>
+  <si>
+    <t>Mensagem exibida: "Esta consulta já está com pagamento confirmado."</t>
+  </si>
+  <si>
+    <t>CT10 - Sessão de Pagamento Expirada</t>
+  </si>
+  <si>
+    <t>1. Iniciar pagamento.2. Aguardar mais de 15 minutos sem ação.</t>
+  </si>
+  <si>
+    <t>Sessão inativa por &gt; 15 min</t>
+  </si>
+  <si>
+    <t>Sessão expira e sistema exige reinício do processo de pagamento.</t>
+  </si>
+  <si>
+    <t>CT11 - Cancelamento Após Prazo</t>
+  </si>
+  <si>
+    <t>1. Tentar cancelar consulta com menos de 24h de antecedência.</t>
+  </si>
+  <si>
+    <t>Consulta fora do prazo</t>
+  </si>
+  <si>
+    <t>Sistema informa sobre possível multa conforme política da clínica.</t>
+  </si>
+  <si>
+    <t>CT12 - Atualização da Tabela</t>
+  </si>
+  <si>
+    <t>1. Concluir cancelamento ou pagamento.</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Tabela de consultas atualizada automaticamente com novo status.</t>
+  </si>
+  <si>
+    <t>CT13 - Geração de Log Financeiro</t>
+  </si>
+  <si>
+    <t>1. Realizar um pagamento com sucesso.</t>
+  </si>
+  <si>
+    <t>Dados de pagamento válidos</t>
+  </si>
+  <si>
+    <t>Log financeiro gerado para a transação.</t>
+  </si>
+  <si>
+    <t>CT14 - Envio de Notificações</t>
+  </si>
+  <si>
+    <t>1. Cancelar ou pagar uma consulta.</t>
+  </si>
+  <si>
+    <t>E-mail enviado automaticamente ao paciente e à clínica.</t>
+  </si>
+  <si>
+    <t>CT15 - Segurança de Dados no Pagamento</t>
+  </si>
+  <si>
+    <t>1. Realizar pagamento.</t>
+  </si>
+  <si>
+    <t>Dados do cartão</t>
+  </si>
+  <si>
+    <t>Dados sensíveis não armazenados. Transação realizada via tokenização.</t>
+  </si>
+  <si>
+    <t>V2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -236,30 +241,21 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -271,7 +267,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -279,119 +275,95 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -444,28 +416,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.12"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.94"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="11.53"/>
+    <col min="1" max="1" width="16" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" style="1"/>
+    <col min="6" max="6" width="13.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -487,8 +458,11 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H1" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -504,8 +478,11 @@
       <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -521,8 +498,11 @@
       <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
@@ -538,8 +518,11 @@
       <c r="F4" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
@@ -555,8 +538,11 @@
       <c r="F5" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
@@ -572,8 +558,11 @@
       <c r="F6" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>27</v>
       </c>
@@ -589,8 +578,11 @@
       <c r="F7" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>31</v>
       </c>
@@ -606,8 +598,11 @@
       <c r="F8" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>35</v>
       </c>
@@ -623,8 +618,11 @@
       <c r="F9" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>39</v>
       </c>
@@ -640,8 +638,11 @@
       <c r="F10" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H10" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>43</v>
       </c>
@@ -657,8 +658,11 @@
       <c r="F11" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>47</v>
       </c>
@@ -674,8 +678,11 @@
       <c r="F12" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>51</v>
       </c>
@@ -691,8 +698,11 @@
       <c r="F13" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H13" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>55</v>
       </c>
@@ -708,8 +718,11 @@
       <c r="F14" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>59</v>
       </c>
@@ -725,8 +738,11 @@
       <c r="F15" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>62</v>
       </c>
@@ -742,12 +758,14 @@
       <c r="F16" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="H16" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
   </headerFooter>
